--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -14,24 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>username</t>
   </si>
   <si>
     <t>password</t>
-  </si>
-  <si>
-    <t>user1</t>
-  </si>
-  <si>
-    <t>pass1</t>
-  </si>
-  <si>
-    <t>user2</t>
-  </si>
-  <si>
-    <t>pass2</t>
   </si>
   <si>
     <t>admin@yourstore.com</t>
@@ -390,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -406,32 +394,16 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -22,10 +22,10 @@
     <t>password</t>
   </si>
   <si>
-    <t>admin@yourstore.com</t>
+    <t>standard_user</t>
   </si>
   <si>
-    <t>admin…</t>
+    <t>my_secret_code</t>
   </si>
 </sst>
 </file>
@@ -41,9 +41,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,16 +66,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -382,19 +380,19 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -403,8 +401,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId1" display="admin@yourstore.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>